--- a/planilha_padrao_atualizada.xlsx
+++ b/planilha_padrao_atualizada.xlsx
@@ -752,7 +752,7 @@
         <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>20</v>
@@ -764,7 +764,7 @@
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>4</v>
@@ -878,7 +878,7 @@
         <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
         <v>4</v>
@@ -992,7 +992,7 @@
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>4</v>
@@ -1106,7 +1106,7 @@
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
         <v>4</v>
@@ -1220,7 +1220,7 @@
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>4</v>
@@ -1334,7 +1334,7 @@
         <v>100</v>
       </c>
       <c r="O9" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
         <v>4</v>
@@ -1448,7 +1448,7 @@
         <v>100</v>
       </c>
       <c r="O10" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
         <v>4</v>
@@ -1562,7 +1562,7 @@
         <v>100</v>
       </c>
       <c r="O11" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
         <v>4</v>
@@ -1676,7 +1676,7 @@
         <v>100</v>
       </c>
       <c r="O12" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="P12" t="n">
         <v>4</v>
@@ -1790,7 +1790,7 @@
         <v>100</v>
       </c>
       <c r="O13" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="P13" t="n">
         <v>4</v>
